--- a/data/trans_camb/DCD-Edad-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,29</t>
+          <t>-2,3; 0,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,71</t>
+          <t>-1,31; 3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,34</t>
+          <t>-3,85; 1,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 18,73</t>
+          <t>5,86; 18,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,5</t>
+          <t>-2,59; 0,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,16</t>
+          <t>2,64; 8,83</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 187,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 45,23</t>
+          <t>-62,38; 47,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88,17; 525,06</t>
+          <t>91,85; 525,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 29,44</t>
+          <t>-68,8; 14,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,47; 340,25</t>
+          <t>59,72; 360,94</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,48</t>
+          <t>-1,41; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,35</t>
+          <t>-0,23; 5,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,95</t>
+          <t>-3,15; 3,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,88</t>
+          <t>0,55; 10,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,99</t>
+          <t>-1,52; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,06</t>
+          <t>1,75; 7,35</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 136,03</t>
+          <t>-44,7; 132,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 295,05</t>
+          <t>-15,69; 284,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 59,24</t>
+          <t>-38,11; 58,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 173,73</t>
+          <t>6,73; 184,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 51,69</t>
+          <t>-28,13; 53,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,54; 184,77</t>
+          <t>32,97; 186,57</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,84</t>
+          <t>-2,44; 1,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,61</t>
+          <t>0,63; 6,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,36</t>
+          <t>-6,31; 0,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,97</t>
+          <t>-0,55; 8,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,2</t>
+          <t>-3,75; 0,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,37</t>
+          <t>1,25; 6,36</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 59,98</t>
+          <t>-46,73; 60,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,4; 206,78</t>
+          <t>8,42; 203,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 4,96</t>
+          <t>-46,59; 7,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 79,85</t>
+          <t>-3,72; 80,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 3,27</t>
+          <t>-40,75; 5,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,4; 90,57</t>
+          <t>14,51; 89,71</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,58</t>
+          <t>-3,07; 2,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 8,36</t>
+          <t>-2,97; 8,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 2,29</t>
+          <t>-5,78; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 13,6</t>
+          <t>4,71; 13,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,67</t>
+          <t>-3,48; 1,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,4</t>
+          <t>-1,05; 9,86</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 47,73</t>
+          <t>-37,18; 50,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 145,36</t>
+          <t>-36,13; 155,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 19,21</t>
+          <t>-34,91; 17,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,58; 111,31</t>
+          <t>28,82; 110,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 18,39</t>
+          <t>-28,71; 17,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 94,35</t>
+          <t>-7,45; 98,96</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 7,81</t>
+          <t>-0,62; 7,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,81</t>
+          <t>7,27; 16,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,21</t>
+          <t>-9,02; 1,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 15,02</t>
+          <t>5,45; 15,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,4</t>
+          <t>-3,77; 3,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,72</t>
+          <t>7,47; 14,23</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 119,4</t>
+          <t>-6,33; 116,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>64,86; 244,2</t>
+          <t>63,76; 239,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 12,61</t>
+          <t>-36,35; 8,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,92; 83,2</t>
+          <t>22,11; 82,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 25,26</t>
+          <t>-21,81; 27,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,94; 104,31</t>
+          <t>42,71; 107,89</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 0,18</t>
+          <t>-10,76; 0,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 7,75</t>
+          <t>-2,9; 7,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,29; -4,29</t>
+          <t>-16,72; -3,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 6,63</t>
+          <t>-21,34; 7,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -4,6</t>
+          <t>-12,23; -4,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 5,29</t>
+          <t>-12,66; 5,46</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 3,66</t>
+          <t>-58,3; 3,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 64,13</t>
+          <t>-15,57; 67,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,18; -17,6</t>
+          <t>-53,17; -15,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,91; 24,7</t>
+          <t>-67,11; 26,27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,7; -22,43</t>
+          <t>-50,77; -22,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 25,27</t>
+          <t>-51,7; 26,01</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 6,65</t>
+          <t>-7,41; 7,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,16; 16,26</t>
+          <t>2,96; 16,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -1,96</t>
+          <t>-16,9; -2,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,76; 18,07</t>
+          <t>6,02; 18,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -1,21</t>
+          <t>-11,29; -0,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,87; 15,55</t>
+          <t>5,42; 15,34</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 40,74</t>
+          <t>-31,02; 45,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,46; 98,96</t>
+          <t>11,47; 102,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,03; -5,61</t>
+          <t>-40,09; -6,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13,34; 52,43</t>
+          <t>13,64; 53,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-34,01; -4,25</t>
+          <t>-33,26; -3,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,54; 54,43</t>
+          <t>15,98; 56,08</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,27</t>
+          <t>-1,14; 1,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,39</t>
+          <t>3,17; 7,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,64</t>
+          <t>-4,89; -1,35</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,33</t>
+          <t>3,34; 10,44</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,52</t>
+          <t>-2,7; -0,54</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,52</t>
+          <t>4,33; 8,54</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 21,11</t>
+          <t>-15,52; 22,46</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>43,17; 120,6</t>
+          <t>47,99; 122,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,28; -10,49</t>
+          <t>-28,61; -8,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20,95; 66,58</t>
+          <t>20,81; 66,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -5,09</t>
+          <t>-22,25; -4,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>39,12; 76,38</t>
+          <t>36,65; 77,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DCD-Edad-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,25</t>
+          <t>11,98</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>5,84</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,29</t>
+          <t>-2,03; 0,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,65</t>
+          <t>-1,35; 3,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,32</t>
+          <t>-4,23; 1,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 18,97</t>
+          <t>6,56; 18,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,25</t>
+          <t>-2,67; 0,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,83</t>
+          <t>2,95; 9,64</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>233,7%</t>
+          <t>248,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>172,03%</t>
+          <t>196,82%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 211,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 537,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 47,24</t>
+          <t>-63,67; 48,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,85; 525,91</t>
+          <t>95,68; 508,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,8; 14,46</t>
+          <t>-68,57; 15,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,72; 360,94</t>
+          <t>84,02; 410,98</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,87</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,66</t>
+          <t>-1,62; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 5,41</t>
+          <t>-0,34; 5,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,04</t>
+          <t>-3,06; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 10,24</t>
+          <t>2,98; 11,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,94</t>
+          <t>-1,58; 1,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,35</t>
+          <t>2,7; 7,53</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>103,89%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>105,29%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 132,07</t>
+          <t>-48,69; 124,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 284,25</t>
+          <t>-13,27; 253,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 58,61</t>
+          <t>-36,78; 55,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 184,44</t>
+          <t>34,73; 215,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 53,55</t>
+          <t>-28,06; 48,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,97; 186,57</t>
+          <t>44,67; 190,82</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>2,69</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>4,27</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,89</t>
+          <t>-2,78; 1,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,39</t>
+          <t>0,09; 5,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 0,7</t>
+          <t>-6,11; 0,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 8,05</t>
+          <t>2,43; 9,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,32</t>
+          <t>-3,83; 0,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,36</t>
+          <t>2,01; 6,68</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 60,0</t>
+          <t>-49,67; 59,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,42; 203,56</t>
+          <t>0,26; 180,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 7,69</t>
+          <t>-44,07; 7,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 80,98</t>
+          <t>17,76; 97,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,75; 5,16</t>
+          <t>-41,11; 2,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,51; 89,71</t>
+          <t>21,94; 93,82</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,51</t>
+          <t>6,98</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,23</t>
+          <t>10,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>8,72</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,58</t>
+          <t>-3,02; 2,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 8,8</t>
+          <t>3,85; 10,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 2,16</t>
+          <t>-5,51; 2,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,44</t>
+          <t>6,11; 14,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,55</t>
+          <t>-3,24; 1,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,86</t>
+          <t>6,35; 11,4</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>105,44%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 50,39</t>
+          <t>-36,21; 55,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 155,04</t>
+          <t>47,01; 213,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 17,42</t>
+          <t>-33,43; 20,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,82; 110,11</t>
+          <t>36,0; 118,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 17,12</t>
+          <t>-27,58; 20,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 98,96</t>
+          <t>52,59; 125,59</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,53</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,35</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,74</t>
+          <t>10,31</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,62</t>
+          <t>-0,81; 7,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,03</t>
+          <t>6,92; 15,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 1,55</t>
+          <t>-8,57; 2,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 15,15</t>
+          <t>5,35; 15,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,79</t>
+          <t>-3,61; 3,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 14,23</t>
+          <t>6,95; 13,52</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>132,72%</t>
+          <t>124,68%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 116,1</t>
+          <t>-11,1; 110,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>63,76; 239,34</t>
+          <t>61,9; 230,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 8,86</t>
+          <t>-36,25; 11,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,11; 82,2</t>
+          <t>20,62; 81,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 27,4</t>
+          <t>-20,9; 26,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,71; 107,89</t>
+          <t>38,87; 100,44</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 0,17</t>
+          <t>-11,24; -0,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,81</t>
+          <t>-3,34; 8,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -3,98</t>
+          <t>-16,75; -4,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 7,13</t>
+          <t>-0,63; 11,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,23; -4,2</t>
+          <t>-12,9; -4,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 5,46</t>
+          <t>0,03; 7,88</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-22,49%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-7,03%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-58,3; 3,26</t>
+          <t>-61,53; -1,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 67,85</t>
+          <t>-17,12; 71,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -15,54</t>
+          <t>-53,09; -18,31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-67,11; 26,27</t>
+          <t>-2,03; 46,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-50,77; -22,07</t>
+          <t>-51,73; -21,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 26,01</t>
+          <t>-0,99; 41,12</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11,92</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,94</t>
+          <t>11,33</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 7,06</t>
+          <t>-7,9; 5,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,13</t>
+          <t>2,38; 16,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,9; -2,21</t>
+          <t>-17,22; -2,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,37</t>
+          <t>6,41; 18,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,92</t>
+          <t>-11,29; -0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,34</t>
+          <t>6,9; 16,01</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 45,26</t>
+          <t>-32,7; 36,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11,47; 102,33</t>
+          <t>9,21; 105,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,09; -6,43</t>
+          <t>-40,66; -8,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13,64; 53,86</t>
+          <t>14,78; 56,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,26; -3,31</t>
+          <t>-33,39; -2,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,98; 56,08</t>
+          <t>20,21; 56,64</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>8,41</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,35</t>
+          <t>-1,08; 1,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,52</t>
+          <t>4,95; 7,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -1,35</t>
+          <t>-5,02; -1,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,44</t>
+          <t>8,45; 12,13</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,54</t>
+          <t>-2,7; -0,6</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,54</t>
+          <t>7,32; 9,51</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 22,46</t>
+          <t>-14,89; 21,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>47,99; 122,91</t>
+          <t>68,58; 129,6</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-28,61; -8,96</t>
+          <t>-29,02; -10,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20,81; 66,42</t>
+          <t>47,92; 78,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -4,52</t>
+          <t>-22,21; -5,48</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,65; 77,53</t>
+          <t>60,05; 85,97</t>
         </is>
       </c>
     </row>
